--- a/R Markdown/resultados/regionalizacao_acoes_2024.xlsx
+++ b/R Markdown/resultados/regionalizacao_acoes_2024.xlsx
@@ -880,13 +880,13 @@
         <v>2024</v>
       </c>
       <c r="C24">
-        <v>825431268.3099999</v>
+        <v>825431268.3100001</v>
       </c>
       <c r="D24">
         <v>5926085.37</v>
       </c>
       <c r="E24">
-        <v>0.00717938076435262</v>
+        <v>0.007179380764352619</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -1012,13 +1012,13 @@
         <v>2024</v>
       </c>
       <c r="C30">
-        <v>622587410.8</v>
+        <v>622587410.8000001</v>
       </c>
       <c r="D30">
         <v>622318055.41</v>
       </c>
       <c r="E30">
-        <v>0.9995673613289837</v>
+        <v>0.9995673613289835</v>
       </c>
       <c r="F30">
         <v>32</v>
@@ -6801,7 +6801,7 @@
         <v>2024</v>
       </c>
       <c r="C293">
-        <v>2883697.49</v>
+        <v>2862697.49</v>
       </c>
       <c r="D293">
         <v>0</v>
